--- a/artfynd/A 59298-2021 artfynd.xlsx
+++ b/artfynd/A 59298-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59298-2021 artfynd.xlsx
+++ b/artfynd/A 59298-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56017095</v>
+        <v>56017098</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>833891.0706754155</v>
+        <v>833860</v>
       </c>
       <c r="R2" t="n">
-        <v>7332372.181184028</v>
+        <v>7332426</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2015-10-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-10-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56017097</v>
+        <v>129763276</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>388</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brännan, Nb</t>
+          <t>Vitåskogen, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>833859.9855798106</v>
+        <v>833680</v>
       </c>
       <c r="R3" t="n">
-        <v>7332426.151481333</v>
+        <v>7332222</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-10-19</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-10-19</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,31 +867,30 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per-Anders Jonsson, Camilla Carlsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56017093</v>
+        <v>56016734</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -939,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>833890.2598951254</v>
+        <v>833687</v>
       </c>
       <c r="R4" t="n">
-        <v>7332288.105185742</v>
+        <v>7332337</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -969,22 +948,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-10-19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-10-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,16 +983,11 @@
         <v>56017091</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1051,10 +1015,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>833763.2655900617</v>
+        <v>833763</v>
       </c>
       <c r="R5" t="n">
-        <v>7332264.090933602</v>
+        <v>7332264</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1084,19 +1048,9 @@
           <t>2015-10-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-10-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,19 +1077,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56016734</v>
+        <v>56017093</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1163,10 +1112,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>833687.0867527018</v>
+        <v>833890</v>
       </c>
       <c r="R6" t="n">
-        <v>7332337.04295107</v>
+        <v>7332288</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1193,22 +1142,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-10-15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-10-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1174,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56017092</v>
+        <v>56017095</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>833763.2655900617</v>
+        <v>833891</v>
       </c>
       <c r="R7" t="n">
-        <v>7332264.090933602</v>
+        <v>7332372</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1308,19 +1242,9 @@
           <t>2015-10-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2015-10-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1271,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56017098</v>
+        <v>56017097</v>
       </c>
       <c r="B8" t="n">
-        <v>78472</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>833859.9855798106</v>
+        <v>833860</v>
       </c>
       <c r="R8" t="n">
-        <v>7332426.151481333</v>
+        <v>7332426</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1420,19 +1339,9 @@
           <t>2015-10-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2015-10-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,53 +1368,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>56016735</v>
+        <v>129763293</v>
       </c>
       <c r="B9" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Brännan, Nb</t>
+          <t>Vitåskogen, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>833687.0867527018</v>
+        <v>833680</v>
       </c>
       <c r="R9" t="n">
-        <v>7332337.04295107</v>
+        <v>7332222</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,22 +1433,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2015-10-15</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2015-10-15</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,15 +1463,116 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>56016735</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Brännan, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>833687</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7332337</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2015-10-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2015-10-15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Sture Westerberg</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Per-Anders Jonsson, Camilla Carlsson</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59298-2021 artfynd.xlsx
+++ b/artfynd/A 59298-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56017098</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129763276</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016734</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56017091</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56017093</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,6 +1298,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56017095</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1365,6 +1400,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56017097</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129763293</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1573,8 +1618,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016735</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>